--- a/master/result/72_重生校园：青春恋曲/72_青春校园_爱在毕业季.xlsx
+++ b/master/result/72_重生校园：青春恋曲/72_青春校园_爱在毕业季.xlsx
@@ -397,423 +397,535 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D37"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>imagination</v>
       </c>
       <c r="B2" t="str">
-        <v>imagination</v>
+        <v>/imagination/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>想象力</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>west</v>
       </c>
       <c r="B3" t="str">
-        <v>west</v>
+        <v>/west/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>西方</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>sacred</v>
       </c>
       <c r="B4" t="str">
-        <v>sacred</v>
+        <v>/sacred/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>神圣的</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>instruction</v>
       </c>
       <c r="B5" t="str">
-        <v>instruction</v>
+        <v>/instruction/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>指导</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>smell</v>
       </c>
       <c r="B6" t="str">
-        <v>smell</v>
+        <v>/smel/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>气味</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>champion</v>
       </c>
       <c r="B7" t="str">
-        <v>champion</v>
+        <v>/ˈtʃæmpiən/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>冠军</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>awkward</v>
       </c>
       <c r="B8" t="str">
-        <v>awkward</v>
+        <v>/awkward/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>尴尬</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>smile</v>
       </c>
       <c r="B9" t="str">
-        <v>smile</v>
+        <v>/smaɪl/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>微笑</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>somewhere</v>
       </c>
       <c r="B10" t="str">
-        <v>somewhere</v>
+        <v>/somewhere/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>某地</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>exhibition</v>
       </c>
       <c r="B11" t="str">
-        <v>exhibition</v>
+        <v>/exhibition/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>展览</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>deer</v>
       </c>
       <c r="B12" t="str">
-        <v>deer</v>
+        <v>/deer/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>鹿</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>aesthetic</v>
       </c>
       <c r="B13" t="str">
-        <v>aesthetic</v>
+        <v>/aesthetic/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>审美</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>dress</v>
       </c>
       <c r="B14" t="str">
-        <v>dress</v>
+        <v>/dres/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>裙子</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>highlight</v>
       </c>
       <c r="B15" t="str">
-        <v>highlight</v>
+        <v>/highlight/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>部分</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>urban</v>
       </c>
       <c r="B16" t="str">
-        <v>urban</v>
+        <v>/urban/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>城市</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>remote</v>
       </c>
       <c r="B17" t="str">
-        <v>remote</v>
+        <v>/remote/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>遥远</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>his</v>
       </c>
       <c r="B18" t="str">
-        <v>his</v>
+        <v>/his/</v>
       </c>
       <c r="C18" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>他的</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>case</v>
       </c>
       <c r="B19" t="str">
-        <v>case</v>
+        <v>/case/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>情况</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>palm</v>
       </c>
       <c r="B20" t="str">
-        <v>palm</v>
+        <v>/palm/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>手掌</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>score</v>
       </c>
       <c r="B21" t="str">
-        <v>score</v>
+        <v>/score/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>分数</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>tape</v>
       </c>
       <c r="B22" t="str">
-        <v>tape</v>
+        <v>/tape/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>磁带</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>linen</v>
       </c>
       <c r="B23" t="str">
-        <v>linen</v>
+        <v>/linen/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>亚麻布</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>quiver</v>
       </c>
       <c r="B24" t="str">
-        <v>quiver</v>
+        <v>/quiver/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>颤抖</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>compatible</v>
       </c>
       <c r="B25" t="str">
-        <v>compatible</v>
+        <v>/compatible/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>合得来</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>partner</v>
       </c>
       <c r="B26" t="str">
-        <v>partner</v>
+        <v>/partner/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>伴侣</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>eager</v>
       </c>
       <c r="B27" t="str">
-        <v>eager</v>
+        <v>/eager/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>渴望</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>percent</v>
       </c>
       <c r="B28" t="str">
-        <v>percent</v>
+        <v>/percent/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>百分之</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>call</v>
       </c>
       <c r="B29" t="str">
-        <v>call</v>
+        <v>/kɔːl/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>打电话</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>argument</v>
       </c>
       <c r="B30" t="str">
-        <v>argument</v>
+        <v>/ˈɑːɡjʊmənt/</v>
       </c>
       <c r="C30" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>论点</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>function</v>
       </c>
       <c r="B31" t="str">
-        <v>function</v>
+        <v>/function/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>功能</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>descend</v>
       </c>
       <c r="B32" t="str">
-        <v>descend</v>
+        <v>/descend/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>下来</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>realm</v>
       </c>
       <c r="B33" t="str">
-        <v>realm</v>
+        <v>/realm/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>领域</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>unload</v>
       </c>
       <c r="B34" t="str">
-        <v>unload</v>
+        <v>/unload/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>卸货</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>graduate</v>
       </c>
       <c r="B35" t="str">
-        <v>graduate</v>
+        <v>/ˈɡrædʒʊeɪt/</v>
       </c>
       <c r="C35" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D35" t="str">
         <v>毕业生</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>ownership</v>
       </c>
       <c r="B36" t="str">
-        <v>ownership</v>
+        <v>/ownership/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>所有物</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>disposition</v>
       </c>
       <c r="B37" t="str">
-        <v>disposition</v>
+        <v>/disposition/</v>
       </c>
       <c r="C37" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>倾向</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D37"/>
   </ignoredErrors>
 </worksheet>
 </file>